--- a/cet4/result/50_体育女神_排球少女的逆袭路/50_体育女神_排球少女的逆袭路_学习版.xlsx
+++ b/cet4/result/50_体育女神_排球少女的逆袭路/50_体育女神_排球少女的逆袭路_学习版.xlsx
@@ -397,815 +397,619 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D43"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>September</v>
       </c>
       <c r="B2" t="str">
-        <v>September</v>
+        <v>/sepˈtembər/</v>
       </c>
       <c r="C2" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>九月</v>
       </c>
-      <c r="D2" t="str">
-        <v>September(九月)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>volleyball</v>
       </c>
       <c r="B3" t="str">
-        <v>volleyball</v>
+        <v>/ˈvɑːlibɔːl/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>排球</v>
       </c>
-      <c r="D3" t="str">
-        <v>volleyball(排球)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>farm</v>
       </c>
       <c r="B4" t="str">
-        <v>farm</v>
+        <v>/fɑːrm/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D4" t="str">
         <v>农场</v>
       </c>
-      <c r="D4" t="str">
-        <v>farm(农场)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>freedom</v>
       </c>
       <c r="B5" t="str">
-        <v>freedom</v>
+        <v>/ˈfriːdəm/</v>
       </c>
       <c r="C5" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>自由</v>
       </c>
-      <c r="D5" t="str">
-        <v>freedom(自由)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>traditional</v>
       </c>
       <c r="B6" t="str">
-        <v>traditional</v>
+        <v>/trəˈdɪʃənl/</v>
       </c>
       <c r="C6" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D6" t="str">
         <v>传统的</v>
       </c>
-      <c r="D6" t="str">
-        <v>traditional(传统的)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>noble</v>
       </c>
       <c r="B7" t="str">
-        <v>noble</v>
+        <v>/ˈnoʊbl/</v>
       </c>
       <c r="C7" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D7" t="str">
         <v>高尚的</v>
       </c>
-      <c r="D7" t="str">
-        <v>noble(高尚的)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>loyalty</v>
       </c>
       <c r="B8" t="str">
-        <v>loyalty</v>
+        <v>/ˈlɔɪəlti/</v>
       </c>
       <c r="C8" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>忠诚</v>
       </c>
-      <c r="D8" t="str">
-        <v>loyalty(忠诚)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>diligent</v>
       </c>
       <c r="B9" t="str">
-        <v>diligent</v>
+        <v>/ˈdɪlɪdʒənt/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D9" t="str">
         <v>勤勉的</v>
       </c>
-      <c r="D9" t="str">
-        <v>diligent(勤勉的)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>desk</v>
       </c>
       <c r="B10" t="str">
-        <v>desk</v>
+        <v>/desk/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D10" t="str">
         <v>桌子</v>
       </c>
-      <c r="D10" t="str">
-        <v>desk(桌子)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>stab</v>
       </c>
       <c r="B11" t="str">
-        <v>stab</v>
+        <v>/stæb/</v>
       </c>
       <c r="C11" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D11" t="str">
         <v>刺</v>
       </c>
-      <c r="D11" t="str">
-        <v>stab(刺)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>better</v>
       </c>
       <c r="B12" t="str">
-        <v>better</v>
+        <v>/ˈbetər/</v>
       </c>
       <c r="C12" t="str">
+        <v>v./adj./adv.</v>
+      </c>
+      <c r="D12" t="str">
         <v>更好的</v>
       </c>
-      <c r="D12" t="str">
-        <v>better(更好的)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>humorous</v>
       </c>
       <c r="B13" t="str">
-        <v>humorous</v>
+        <v>/ˈhjuːmərəs/</v>
       </c>
       <c r="C13" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D13" t="str">
         <v>幽默的</v>
       </c>
-      <c r="D13" t="str">
-        <v>humorous(幽默的)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>cigarette</v>
       </c>
       <c r="B14" t="str">
-        <v>cigarette</v>
+        <v>/ˈsɪɡəret/</v>
       </c>
       <c r="C14" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>香烟</v>
       </c>
-      <c r="D14" t="str">
-        <v>cigarette(香烟)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>skin</v>
       </c>
       <c r="B15" t="str">
-        <v>skin</v>
+        <v>/skɪn/</v>
       </c>
       <c r="C15" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D15" t="str">
         <v>皮肤</v>
       </c>
-      <c r="D15" t="str">
-        <v>skin(皮肤)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>actually</v>
       </c>
       <c r="B16" t="str">
-        <v>actually</v>
+        <v>/ˈæktʃuəli/</v>
       </c>
       <c r="C16" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D16" t="str">
         <v>实际上</v>
       </c>
-      <c r="D16" t="str">
-        <v>actually(实际上)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>gentle</v>
       </c>
       <c r="B17" t="str">
-        <v>gentle</v>
+        <v>/ˈdʒentl/</v>
       </c>
       <c r="C17" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D17" t="str">
         <v>温和的</v>
       </c>
-      <c r="D17" t="str">
-        <v>gentle(温和的)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>nucleus</v>
       </c>
       <c r="B18" t="str">
-        <v>nucleus</v>
+        <v>/ˈnuːkliəs/</v>
       </c>
       <c r="C18" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D18" t="str">
         <v>核心</v>
       </c>
-      <c r="D18" t="str">
-        <v>nucleus(核心)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>selection</v>
       </c>
       <c r="B19" t="str">
-        <v>selection</v>
+        <v>/sɪˈlekʃn/</v>
       </c>
       <c r="C19" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D19" t="str">
         <v>选择</v>
       </c>
-      <c r="D19" t="str">
-        <v>selection(选择)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>deck</v>
       </c>
       <c r="B20" t="str">
-        <v>deck</v>
+        <v>/dek/</v>
       </c>
       <c r="C20" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D20" t="str">
         <v>甲板</v>
       </c>
-      <c r="D20" t="str">
-        <v>deck(甲板)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>relax</v>
       </c>
       <c r="B21" t="str">
-        <v>relax</v>
+        <v>/rɪˈlæks/</v>
       </c>
       <c r="C21" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D21" t="str">
         <v>放松</v>
       </c>
-      <c r="D21" t="str">
-        <v>relax(放松)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>Germany</v>
       </c>
       <c r="B22" t="str">
-        <v>Germany</v>
+        <v>/ˈdʒɜːrməni/</v>
       </c>
       <c r="C22" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D22" t="str">
         <v>德国</v>
       </c>
-      <c r="D22" t="str">
-        <v>Germany(德国)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>this</v>
       </c>
       <c r="B23" t="str">
-        <v>this</v>
+        <v>/ðɪs/</v>
       </c>
       <c r="C23" t="str">
+        <v>n./v./adj./adv./pron.</v>
+      </c>
+      <c r="D23" t="str">
         <v>这</v>
       </c>
-      <c r="D23" t="str">
-        <v>this(这)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>modify</v>
       </c>
       <c r="B24" t="str">
-        <v>traditional</v>
+        <v>/ˈmɑːdɪfaɪ/</v>
       </c>
       <c r="C24" t="str">
-        <v>传统的</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D24" t="str">
-        <v>traditional(传统的)📢</v>
+        <v>修改</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>steel</v>
       </c>
       <c r="B25" t="str">
-        <v>modify</v>
+        <v>/stiːl/</v>
       </c>
       <c r="C25" t="str">
-        <v>修改</v>
+        <v>n./vt./adj.</v>
       </c>
       <c r="D25" t="str">
-        <v>modify(修改)📢</v>
+        <v>钢铁</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>twinkle</v>
       </c>
       <c r="B26" t="str">
-        <v>steel</v>
+        <v>/ˈtwɪŋkl/</v>
       </c>
       <c r="C26" t="str">
-        <v>钢铁</v>
+        <v>n./v.</v>
       </c>
       <c r="D26" t="str">
-        <v>steel(钢铁)📢</v>
+        <v>闪烁</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>ninth</v>
       </c>
       <c r="B27" t="str">
-        <v>twinkle</v>
+        <v>/naɪnθ/</v>
       </c>
       <c r="C27" t="str">
-        <v>闪烁</v>
+        <v>n./adj./num.</v>
       </c>
       <c r="D27" t="str">
-        <v>twinkle(闪烁)📢</v>
+        <v>第九</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>high</v>
       </c>
       <c r="B28" t="str">
-        <v>ninth</v>
+        <v>/haɪ/</v>
       </c>
       <c r="C28" t="str">
-        <v>第九</v>
+        <v>n./v./adj./adv.</v>
       </c>
       <c r="D28" t="str">
-        <v>ninth(第九)📢</v>
+        <v>高的</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>clasp</v>
       </c>
       <c r="B29" t="str">
-        <v>high</v>
+        <v>/klæsp/</v>
       </c>
       <c r="C29" t="str">
-        <v>高的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D29" t="str">
-        <v>high(高的)📢</v>
+        <v>紧握</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>unusually</v>
       </c>
       <c r="B30" t="str">
-        <v>clasp</v>
+        <v>/ʌnˈjuːʒuəli/</v>
       </c>
       <c r="C30" t="str">
-        <v>紧握</v>
+        <v>v./adv.</v>
       </c>
       <c r="D30" t="str">
-        <v>clasp(紧握)📢</v>
+        <v>异常地</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>furthermore</v>
       </c>
       <c r="B31" t="str">
-        <v>unusually</v>
+        <v>/ˌfɜːrðərˈmɔːr/</v>
       </c>
       <c r="C31" t="str">
-        <v>异常地</v>
+        <v>v./adv.</v>
       </c>
       <c r="D31" t="str">
-        <v>unusually(异常地)📢</v>
+        <v>此外</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>infant</v>
       </c>
       <c r="B32" t="str">
-        <v>furthermore</v>
+        <v>/ˈɪnfənt/</v>
       </c>
       <c r="C32" t="str">
-        <v>此外</v>
+        <v>n./adj.</v>
       </c>
       <c r="D32" t="str">
-        <v>furthermore(此外)📢</v>
+        <v>婴儿</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>unlikely</v>
       </c>
       <c r="B33" t="str">
-        <v>diligent</v>
+        <v>/ʌnˈlaɪkli/</v>
       </c>
       <c r="C33" t="str">
-        <v>勤勉的</v>
+        <v>v./adj./adv.</v>
       </c>
       <c r="D33" t="str">
-        <v>diligent(勤勉的)📢</v>
+        <v>不太可能的</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>fault</v>
       </c>
       <c r="B34" t="str">
-        <v>infant</v>
+        <v>/fɔːlt/</v>
       </c>
       <c r="C34" t="str">
-        <v>婴儿</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D34" t="str">
-        <v>infant(婴儿)📢</v>
+        <v>故障</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>advisable</v>
       </c>
       <c r="B35" t="str">
-        <v>unlikely</v>
+        <v>/ədˈvaɪzəbl/</v>
       </c>
       <c r="C35" t="str">
-        <v>不太可能的</v>
+        <v>adj.</v>
       </c>
       <c r="D35" t="str">
-        <v>unlikely(不太可能的)📢</v>
+        <v>明智的</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>blank</v>
       </c>
       <c r="B36" t="str">
-        <v>fault</v>
+        <v>/blæŋk/</v>
       </c>
       <c r="C36" t="str">
-        <v>故障</v>
+        <v>n./adj.</v>
       </c>
       <c r="D36" t="str">
-        <v>fault(故障)📢</v>
+        <v>空白的</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>threaten</v>
       </c>
       <c r="B37" t="str">
-        <v>advisable</v>
+        <v>/ˈθretn/</v>
       </c>
       <c r="C37" t="str">
-        <v>明智的</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D37" t="str">
-        <v>advisable(明智的)📢</v>
+        <v>威胁</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>primitive</v>
       </c>
       <c r="B38" t="str">
-        <v>blank</v>
+        <v>/ˈprɪmətɪv/</v>
       </c>
       <c r="C38" t="str">
-        <v>空白的</v>
+        <v>n./adj.</v>
       </c>
       <c r="D38" t="str">
-        <v>blank(空白的)📢</v>
+        <v>原始的</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>stimulate</v>
       </c>
       <c r="B39" t="str">
-        <v>better</v>
+        <v>/ˈstɪmjuleɪt/</v>
       </c>
       <c r="C39" t="str">
-        <v>更好的</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D39" t="str">
-        <v>better(更好的)📢</v>
+        <v>激励</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>throughout</v>
       </c>
       <c r="B40" t="str">
-        <v>threaten</v>
+        <v>/θruːˈaʊt/</v>
       </c>
       <c r="C40" t="str">
-        <v>威胁</v>
+        <v>v./adv./prep.</v>
       </c>
       <c r="D40" t="str">
-        <v>threaten(威胁)📢</v>
+        <v>自始至终</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>towards</v>
       </c>
       <c r="B41" t="str">
-        <v>primitive</v>
+        <v>/tɔːrdz/</v>
       </c>
       <c r="C41" t="str">
-        <v>原始的</v>
+        <v>prep.</v>
       </c>
       <c r="D41" t="str">
-        <v>primitive(原始的)📢</v>
+        <v>朝向</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>translation</v>
       </c>
       <c r="B42" t="str">
-        <v>unlikely</v>
+        <v>/trænzˈleɪʃn/</v>
       </c>
       <c r="C42" t="str">
-        <v>不太可能的</v>
+        <v>n.</v>
       </c>
       <c r="D42" t="str">
-        <v>unlikely(不太可能的)📢</v>
+        <v>翻译</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>lane</v>
       </c>
       <c r="B43" t="str">
-        <v>stimulate</v>
+        <v>/leɪn/</v>
       </c>
       <c r="C43" t="str">
-        <v>激励</v>
+        <v>n.</v>
       </c>
       <c r="D43" t="str">
-        <v>stimulate(激励)📢</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44" t="str">
-        <v>twinkle</v>
-      </c>
-      <c r="C44" t="str">
-        <v>闪烁</v>
-      </c>
-      <c r="D44" t="str">
-        <v>twinkle(闪烁)📢</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45" t="str">
-        <v>throughout</v>
-      </c>
-      <c r="C45" t="str">
-        <v>自始至终</v>
-      </c>
-      <c r="D45" t="str">
-        <v>throughout(自始至终)📢</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="str">
-        <v>better</v>
-      </c>
-      <c r="C46" t="str">
-        <v>更好的</v>
-      </c>
-      <c r="D46" t="str">
-        <v>better(更好的)📢</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="C47" t="str">
-        <v>德国</v>
-      </c>
-      <c r="D47" t="str">
-        <v>Germany(德国)📢</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="str">
-        <v>towards</v>
-      </c>
-      <c r="C48" t="str">
-        <v>朝向</v>
-      </c>
-      <c r="D48" t="str">
-        <v>towards(朝向)📢</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="str">
-        <v>this</v>
-      </c>
-      <c r="C49" t="str">
-        <v>这</v>
-      </c>
-      <c r="D49" t="str">
-        <v>this(这)📢</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="str">
-        <v>noble</v>
-      </c>
-      <c r="C50" t="str">
-        <v>高尚的</v>
-      </c>
-      <c r="D50" t="str">
-        <v>noble(高尚的)📢</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>towards</v>
-      </c>
-      <c r="C51" t="str">
-        <v>朝向</v>
-      </c>
-      <c r="D51" t="str">
-        <v>towards(朝向)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>translation</v>
-      </c>
-      <c r="C52" t="str">
-        <v>翻译</v>
-      </c>
-      <c r="D52" t="str">
-        <v>translation(翻译)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>lane</v>
-      </c>
-      <c r="C53" t="str">
         <v>小巷</v>
-      </c>
-      <c r="D53" t="str">
-        <v>lane(小巷)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>towards</v>
-      </c>
-      <c r="C54" t="str">
-        <v>朝向</v>
-      </c>
-      <c r="D54" t="str">
-        <v>towards(朝向)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>deck</v>
-      </c>
-      <c r="C55" t="str">
-        <v>甲板</v>
-      </c>
-      <c r="D55" t="str">
-        <v>deck(甲板)📢</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>September</v>
-      </c>
-      <c r="C56" t="str">
-        <v>九月</v>
-      </c>
-      <c r="D56" t="str">
-        <v>September(九月)📢</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>volleyball</v>
-      </c>
-      <c r="C57" t="str">
-        <v>排球</v>
-      </c>
-      <c r="D57" t="str">
-        <v>volleyball(排球)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D57"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D43"/>
   </ignoredErrors>
 </worksheet>
 </file>